--- a/data/trans_dic/P19C07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,18</t>
+          <t>1,87; 5,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,15</t>
+          <t>2,28; 5,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,37</t>
+          <t>1,55; 4,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,54</t>
+          <t>2,49; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,62</t>
+          <t>2,31; 5,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,05</t>
+          <t>2,12; 5,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,01</t>
+          <t>3,39; 6,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,35</t>
+          <t>2,39; 5,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,89</t>
+          <t>2,49; 4,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,64</t>
+          <t>2,52; 4,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,11</t>
+          <t>2,77; 4,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,75</t>
+          <t>2,84; 5,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,48</t>
+          <t>2,58; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,3</t>
+          <t>1,78; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,31</t>
+          <t>2,4; 5,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,79</t>
+          <t>1,04; 3,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,07</t>
+          <t>1,75; 4,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,33</t>
+          <t>3,16; 6,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,56</t>
+          <t>2,28; 4,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,0</t>
+          <t>2,6; 5,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,37</t>
+          <t>2,54; 4,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,87</t>
+          <t>2,8; 4,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,5</t>
+          <t>2,59; 4,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,81</t>
+          <t>1,77; 3,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,03</t>
+          <t>2,01; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,36</t>
+          <t>2,23; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,72</t>
+          <t>1,11; 3,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,74</t>
+          <t>3,56; 7,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,27</t>
+          <t>2,04; 5,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,69</t>
+          <t>1,2; 3,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,95</t>
+          <t>2,48; 5,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,32</t>
+          <t>2,16; 6,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,53</t>
+          <t>2,42; 4,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,99</t>
+          <t>1,97; 3,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,29</t>
+          <t>2,23; 4,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,2</t>
+          <t>2,9; 6,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,78</t>
+          <t>2,1; 4,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,08</t>
+          <t>2,41; 5,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,8</t>
+          <t>1,55; 3,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,6</t>
+          <t>1,36; 3,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,52</t>
+          <t>2,79; 5,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,1</t>
+          <t>2,66; 5,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,16</t>
+          <t>1,81; 4,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,22</t>
+          <t>2,7; 5,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,7</t>
+          <t>2,74; 4,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,66</t>
+          <t>2,84; 4,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,74</t>
+          <t>1,92; 3,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,08</t>
+          <t>2,32; 4,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,23</t>
+          <t>2,73; 4,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,04</t>
+          <t>2,71; 4,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,64</t>
+          <t>2,16; 3,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,2</t>
+          <t>2,35; 4,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,27</t>
+          <t>2,81; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,36</t>
+          <t>2,94; 4,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,32</t>
+          <t>2,95; 4,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,7</t>
+          <t>3,07; 4,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,01</t>
+          <t>2,97; 3,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,97</t>
+          <t>2,98; 3,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,72</t>
+          <t>2,76; 3,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,19</t>
+          <t>2,96; 4,15</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9114; 24762</t>
+          <t>8928; 25763</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13427; 31199</t>
+          <t>13816; 32214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8149; 22917</t>
+          <t>8134; 21897</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15627; 46106</t>
+          <t>15233; 47147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12700; 30234</t>
+          <t>12427; 29620</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14747; 32101</t>
+          <t>13454; 31785</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18025; 38162</t>
+          <t>18452; 38067</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15873; 34834</t>
+          <t>15604; 35362</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26054; 49716</t>
+          <t>25247; 50410</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32010; 57583</t>
+          <t>31336; 57484</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30203; 54682</t>
+          <t>29577; 53192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35781; 72651</t>
+          <t>35855; 74445</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18404; 39578</t>
+          <t>18632; 40140</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15123; 37290</t>
+          <t>15425; 37245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19910; 43387</t>
+          <t>19564; 42138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11947; 44181</t>
+          <t>12162; 43273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14592; 32731</t>
+          <t>14059; 34007</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29654; 56909</t>
+          <t>28394; 55062</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19582; 39545</t>
+          <t>19767; 40605</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25341; 47156</t>
+          <t>24466; 47406</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38259; 66689</t>
+          <t>38746; 67142</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50912; 85982</t>
+          <t>49382; 82120</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44474; 75743</t>
+          <t>43517; 75249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37635; 80327</t>
+          <t>37253; 80645</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10707; 27433</t>
+          <t>10979; 27486</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14789; 34109</t>
+          <t>14207; 34659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7014; 20487</t>
+          <t>6106; 20422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24411; 53120</t>
+          <t>24419; 54164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12206; 30834</t>
+          <t>11926; 31002</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8421; 25021</t>
+          <t>8174; 24421</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14628; 34475</t>
+          <t>14371; 34169</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17380; 58312</t>
+          <t>19895; 60056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26287; 51220</t>
+          <t>27393; 53091</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26811; 52436</t>
+          <t>25936; 52215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24661; 48536</t>
+          <t>25187; 48169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45922; 99751</t>
+          <t>46590; 99656</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14851; 33915</t>
+          <t>14883; 32571</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18626; 40891</t>
+          <t>19408; 42697</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12432; 29383</t>
+          <t>12009; 30436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12307; 32029</t>
+          <t>12103; 32493</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22432; 44940</t>
+          <t>22674; 45685</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25029; 47588</t>
+          <t>24824; 49027</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16498; 36458</t>
+          <t>15850; 36296</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28195; 55490</t>
+          <t>28671; 57521</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41324; 71546</t>
+          <t>41686; 69415</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49909; 81080</t>
+          <t>49330; 79755</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32588; 61769</t>
+          <t>31593; 59823</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44985; 79693</t>
+          <t>45209; 79911</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66285; 103953</t>
+          <t>66970; 104631</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78057; 117722</t>
+          <t>78847; 118212</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59575; 96885</t>
+          <t>57493; 93752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80315; 140899</t>
+          <t>78717; 138984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77527; 117081</t>
+          <t>77052; 115636</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92956; 137195</t>
+          <t>92424; 134191</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84044; 123999</t>
+          <t>84665; 123209</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>112051; 168116</t>
+          <t>109933; 165198</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>156069; 208510</t>
+          <t>154068; 205090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183513; 240628</t>
+          <t>180317; 240083</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>153420; 205803</t>
+          <t>152832; 211060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>202167; 290346</t>
+          <t>205341; 288038</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,39</t>
+          <t>2,05; 5,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,32</t>
+          <t>2,28; 5,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,17</t>
+          <t>1,55; 4,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,71</t>
+          <t>2,56; 6,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,5</t>
+          <t>2,39; 5,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,0</t>
+          <t>2,23; 4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,99</t>
+          <t>3,34; 7,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,43</t>
+          <t>2,26; 5,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,96</t>
+          <t>2,6; 4,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,63</t>
+          <t>2,55; 4,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,97</t>
+          <t>2,81; 5,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,9</t>
+          <t>2,72; 5,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,56</t>
+          <t>2,66; 5,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,3</t>
+          <t>1,83; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,16</t>
+          <t>2,44; 5,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,71</t>
+          <t>1,49; 3,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,23</t>
+          <t>1,88; 4,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,13</t>
+          <t>3,22; 6,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,69</t>
+          <t>2,3; 4,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,03</t>
+          <t>2,54; 4,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,4</t>
+          <t>2,51; 4,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,65</t>
+          <t>2,87; 4,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,47</t>
+          <t>2,61; 4,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,82</t>
+          <t>2,26; 3,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,04</t>
+          <t>1,94; 4,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,45</t>
+          <t>2,33; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,71</t>
+          <t>1,25; 3,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,89</t>
+          <t>3,81; 7,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,3</t>
+          <t>2,19; 5,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,6</t>
+          <t>1,21; 3,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,89</t>
+          <t>2,47; 5,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,51</t>
+          <t>4,46; 7,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,7</t>
+          <t>2,33; 4,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,97</t>
+          <t>1,94; 3,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,26</t>
+          <t>2,16; 4,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,2</t>
+          <t>4,65; 7,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,59</t>
+          <t>2,0; 4,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,3</t>
+          <t>2,4; 5,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,94</t>
+          <t>1,6; 3,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,65</t>
+          <t>1,46; 3,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,61</t>
+          <t>2,73; 5,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,25</t>
+          <t>2,68; 5,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,14</t>
+          <t>1,79; 4,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,41</t>
+          <t>3,13; 5,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,56</t>
+          <t>2,74; 4,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,59</t>
+          <t>2,85; 4,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,63</t>
+          <t>1,91; 3,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,09</t>
+          <t>2,55; 4,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,26</t>
+          <t>2,74; 4,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,06</t>
+          <t>2,72; 4,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,52</t>
+          <t>2,26; 3,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,14</t>
+          <t>2,75; 4,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,22</t>
+          <t>2,85; 4,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,27</t>
+          <t>2,98; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,3</t>
+          <t>2,87; 4,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 4,62</t>
+          <t>3,52; 4,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,95</t>
+          <t>2,94; 3,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,96</t>
+          <t>2,99; 3,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,82</t>
+          <t>2,78; 3,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,15</t>
+          <t>3,35; 4,39</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>51400</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8928; 25763</t>
+          <t>9812; 25374</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13816; 32214</t>
+          <t>13837; 32434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8134; 21897</t>
+          <t>8144; 23370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15233; 47147</t>
+          <t>16916; 43282</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12427; 29620</t>
+          <t>12835; 29606</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13454; 31785</t>
+          <t>14193; 31227</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18452; 38067</t>
+          <t>18163; 39566</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15604; 35362</t>
+          <t>15952; 36840</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25247; 50410</t>
+          <t>26443; 48443</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31336; 57484</t>
+          <t>31607; 56797</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29577; 53192</t>
+          <t>30030; 53819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35855; 74445</t>
+          <t>37090; 71482</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>60870</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18632; 40140</t>
+          <t>19203; 42172</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15425; 37245</t>
+          <t>15860; 37839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19564; 42138</t>
+          <t>19940; 43202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12162; 43273</t>
+          <t>15153; 39486</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14059; 34007</t>
+          <t>15114; 33082</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28394; 55062</t>
+          <t>28922; 56043</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19767; 40605</t>
+          <t>19960; 39669</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24466; 47406</t>
+          <t>26647; 50352</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38746; 67142</t>
+          <t>38243; 67070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49382; 82120</t>
+          <t>50611; 84964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43517; 75249</t>
+          <t>43874; 73993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37253; 80645</t>
+          <t>46559; 79132</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>43761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40390</t>
+          <t>46210</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>89971</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10979; 27486</t>
+          <t>10560; 26649</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14207; 34659</t>
+          <t>14850; 35082</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6106; 20422</t>
+          <t>6890; 20484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24419; 54164</t>
+          <t>29501; 60586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11926; 31002</t>
+          <t>12784; 30968</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8174; 24421</t>
+          <t>8215; 24691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14371; 34169</t>
+          <t>14341; 34481</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19895; 60056</t>
+          <t>35469; 60779</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27393; 53091</t>
+          <t>26370; 50513</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25936; 52215</t>
+          <t>25481; 51252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25187; 48169</t>
+          <t>24357; 47818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46590; 99656</t>
+          <t>73043; 112734</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40078</t>
+          <t>45027</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>67685</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14883; 32571</t>
+          <t>14221; 31945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19408; 42697</t>
+          <t>19345; 41057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12009; 30436</t>
+          <t>12372; 29250</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12103; 32493</t>
+          <t>13841; 36790</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22674; 45685</t>
+          <t>22249; 46928</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24824; 49027</t>
+          <t>25031; 49481</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15850; 36296</t>
+          <t>15660; 35968</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28671; 57521</t>
+          <t>33717; 62681</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41686; 69415</t>
+          <t>41743; 71738</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49330; 79755</t>
+          <t>49593; 81742</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31593; 59823</t>
+          <t>31580; 58828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45209; 79911</t>
+          <t>51702; 89278</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107520</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>269926</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66970; 104631</t>
+          <t>67347; 103332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78847; 118212</t>
+          <t>79376; 119741</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57493; 93752</t>
+          <t>60136; 94876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78717; 138984</t>
+          <t>93329; 147596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77052; 115636</t>
+          <t>78134; 115038</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92424; 134191</t>
+          <t>93902; 138327</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84665; 123209</t>
+          <t>82376; 121465</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>109933; 165198</t>
+          <t>127565; 176936</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>154068; 205090</t>
+          <t>152983; 207455</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>180317; 240083</t>
+          <t>181344; 239580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152832; 211060</t>
+          <t>153503; 208873</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>205341; 288038</t>
+          <t>235502; 308107</t>
         </is>
       </c>
     </row>
